--- a/docs/program-audit-2026-10-27.xlsx
+++ b/docs/program-audit-2026-10-27.xlsx
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>生成时间：2026-10-27 19:47　|　范围：C: 与 D: 　|　工具：PowerShell 注册表/文件系统扫描</t>
+          <t>生成时间：2026-10-27 19:57　|　范围：C: 与 D: 　|　工具：PowerShell 注册表/文件系统扫描</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,11 @@
           <t>离线文档 64 MB，网上能查。</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr"/>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -919,7 +923,11 @@
           <t>Python 自带的测试套件 36.8 MB，个人使用不需要。</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -963,7 +971,11 @@
           <t>Outlook 的 Teams 会议插件，没装 Teams 就没用。</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1007,7 +1019,11 @@
           <t>Saber Interactive 游戏遗留的证书更新器，很小但已无用。</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1201,7 +1217,11 @@
           <t>1.38 GB。之前发现它的 WFP 驱动文件已丢失、服务已被禁用，属于半卸载状态；不用建议卸掉，卸载器 D:\Thunder\Program\ThunderUninstall.exe 还在。</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1705,7 +1725,11 @@
           <t>应用软件。</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -3258,7 +3282,11 @@
           <t>离线文档 64 MB，网上能查。</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr"/>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -3303,7 +3331,11 @@
           <t>Python 自带的测试套件 36.8 MB，个人使用不需要。</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -3348,7 +3380,11 @@
           <t>Saber Interactive 游戏遗留的证书更新器，很小但已无用。</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -3432,7 +3468,11 @@
           <t>Outlook 的 Teams 会议插件，没装 Teams 就没用。</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr"/>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -3477,7 +3517,11 @@
           <t>Win11 升级兼容性检查工具，用完就没价值。</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -3522,7 +3566,11 @@
           <t>1.38 GB。之前发现它的 WFP 驱动文件已丢失、服务已被禁用，属于半卸载状态；不用建议卸掉，卸载器 D:\Thunder\Program\ThunderUninstall.exe 还在。</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -3665,7 +3713,11 @@
           <t>应用软件。</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -5033,7 +5085,11 @@
           <t>只做 Windows 桌面开发可卸（MAUI/iOS/tvOS/MacCatalyst 这些 manifest 基本没用上）。</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -5078,7 +5134,11 @@
           <t>只在不跑 .NET 程序时可卸；多数游戏/工具仍依赖 .NET 8/6 运行时。</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -5295,7 +5355,11 @@
           <t>只在不跑 .NET 程序时可卸；多数游戏/工具仍依赖 .NET 8/6 运行时。</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -5340,7 +5404,11 @@
           <t>只在不跑 .NET 程序时可卸；多数游戏/工具仍依赖 .NET 8/6 运行时。</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr"/>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -5385,7 +5453,11 @@
           <t>只在不跑 .NET 程序时可卸；多数游戏/工具仍依赖 .NET 8/6 运行时。</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -5430,7 +5502,11 @@
           <t>只在不跑 .NET 程序时可卸；多数游戏/工具仍依赖 .NET 8/6 运行时。</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr"/>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -5475,7 +5551,11 @@
           <t>只在不跑 .NET 程序时可卸；多数游戏/工具仍依赖 .NET 8/6 运行时。</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -5520,7 +5600,11 @@
           <t>只在不跑 .NET 程序时可卸；多数游戏/工具仍依赖 .NET 8/6 运行时。</t>
         </is>
       </c>
-      <c r="K54" s="7" t="inlineStr"/>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>删除</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
